--- a/survey_templates/041_virtual_counseling_experience_survey--survey_templates.xlsx
+++ b/survey_templates/041_virtual_counseling_experience_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -665,8 +665,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -694,12 +694,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'in-person'}</t>
+          <t>in-person</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'In-person'}</t>
+          <t>In-person</t>
         </is>
       </c>
     </row>
@@ -711,12 +711,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -728,12 +728,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'video'}</t>
+          <t>video</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Video'}</t>
+          <t>Video</t>
         </is>
       </c>
     </row>
@@ -745,12 +745,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'online'}</t>
+          <t>online</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Online'}</t>
+          <t>Online</t>
         </is>
       </c>
     </row>
@@ -762,12 +762,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'technology'}</t>
+          <t>technology</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Technology'}</t>
+          <t>Technology</t>
         </is>
       </c>
     </row>
@@ -779,12 +779,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'communication'}</t>
+          <t>communication</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Communication'}</t>
+          <t>Communication</t>
         </is>
       </c>
     </row>
@@ -796,12 +796,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'availability'}</t>
+          <t>availability</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Availability'}</t>
+          <t>Availability</t>
         </is>
       </c>
     </row>
@@ -813,12 +813,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
